--- a/vk_graph_results/vk_graph_analysis.xlsx
+++ b/vk_graph_results/vk_graph_analysis.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,42 +432,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>degree</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>degree_centrality</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>betweenness_centrality</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>closeness_centrality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>eigenvector_centrality</t>
         </is>
@@ -1316,32 +1328,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name_1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>group_1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>id_2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>name_2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>group_2</t>
         </is>
@@ -1810,27 +1822,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>component_size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
@@ -2439,12 +2451,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>

--- a/vk_graph_results/vk_graph_analysis.xlsx
+++ b/vk_graph_results/vk_graph_analysis.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -694,7 +694,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -994,7 +994,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BSBO-12-26</t>
+          <t>BSMO-12-26</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BSBO-10-26</t>
+          <t>BSMO-11-26</t>
         </is>
       </c>
     </row>
